--- a/output/2026-10-01_21_Malesia_Melaka_Cleaning.xlsx
+++ b/output/2026-10-01_21_Malesia_Melaka_Cleaning.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,6 @@
           <t>+606-317 2948</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Distributore confermato (dal 1959/1965) di material handling equipment, warehouse automation e attrezzature di pulizia industriale, con training e assistenza post-vendita. Filiale Melaka confermata a Jalan Jasa Merdeka 4, Batu Berendam. Email non reperita.</t>
@@ -628,7 +627,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-01_21_Malesia_Melaka_Cleaning.xlsx
+++ b/output/2026-10-01_21_Malesia_Melaka_Cleaning.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore/produttore confermato di prodotti igiene commerciale e janitorial, incl. macchine lavamoquette, aspirapolvere, lavasciuga, idropulitrici, lucidatrici. Sede e contatti confermati.</t>
+          <t>Distributore/produttore confermato di prodotti igiene commerciale e janitorial, incl. macchine lavamoquette, aspirapolvere, lavasciuga, idropulitrici, lucidatrici. Sede e contatti confermati. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fornitore industriale/MRO con catalogo online confermato che include prodotti Karcher (spray extraction cleaner, aspiratori a vapore) e dust collector JETMAC/HITZ, oltre a utensili industriali (Snap-On, Chicago Pneumatic, ecc.). Sede confermata a Taman Puncak Bertam, Melaka.</t>
+          <t>Fornitore industriale/MRO con catalogo online confermato che include prodotti Karcher (spray extraction cleaner, aspiratori a vapore) e dust collector JETMAC/HITZ, oltre a utensili industriali (Snap-On, Chicago Pneumatic, ecc.). Sede confermata a Taman Puncak Bertam, Melaka. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
